--- a/data/trans_bre/P1001-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1001-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 2,18</t>
+          <t>-2,12; 2,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 4,94</t>
+          <t>0,34; 5,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,08</t>
+          <t>-1,32; 3,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 10,89</t>
+          <t>-0,36; 11,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,39; 146,83</t>
+          <t>-58,18; 157,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 401,55</t>
+          <t>4,2; 445,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-47,22; 246,75</t>
+          <t>-42,37; 251,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,74; 1128,44</t>
+          <t>-42,9; 1210,94</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,73</t>
+          <t>1,77; 6,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 4,97</t>
+          <t>0,09; 4,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,66</t>
+          <t>-2,21; 2,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 6,68</t>
+          <t>-0,55; 6,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,32; 292,35</t>
+          <t>37,05; 274,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 268,32</t>
+          <t>-2,65; 244,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 84,76</t>
+          <t>-41,29; 93,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 564,44</t>
+          <t>-22,01; 552,51</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,18</t>
+          <t>-0,06; 5,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 9,26</t>
+          <t>3,05; 9,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,68</t>
+          <t>-0,49; 4,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 2,56</t>
+          <t>-2,88; 2,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 173,67</t>
+          <t>-2,44; 172,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,06; 210,66</t>
+          <t>39,68; 217,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 141,8</t>
+          <t>-9,52; 134,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-39,65; 61,32</t>
+          <t>-37,83; 58,72</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 8,52</t>
+          <t>1,34; 8,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 10,16</t>
+          <t>3,25; 10,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,01; 6,61</t>
+          <t>0,57; 6,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 8,5</t>
+          <t>0,89; 8,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,78; 181,52</t>
+          <t>13,62; 180,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,92; 195,06</t>
+          <t>35,17; 193,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 116,59</t>
+          <t>4,85; 127,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,08; 334,24</t>
+          <t>10,71; 324,41</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 7,0</t>
+          <t>-1,51; 6,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,94; 15,64</t>
+          <t>6,28; 15,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 15,38</t>
+          <t>6,92; 15,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 8,85</t>
+          <t>2,81; 8,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 113,24</t>
+          <t>-15,0; 107,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,56; 207,45</t>
+          <t>52,83; 205,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,35; 283,87</t>
+          <t>77,0; 315,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,5; 152,62</t>
+          <t>30,45; 147,11</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 7,03</t>
+          <t>-3,07; 7,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,9; 16,61</t>
+          <t>4,61; 16,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,27; 18,65</t>
+          <t>7,87; 18,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 8,34</t>
+          <t>-5,21; 8,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 73,68</t>
+          <t>-20,68; 81,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,8; 184,39</t>
+          <t>30,2; 185,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,65; 298,4</t>
+          <t>72,15; 300,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,41; 117,01</t>
+          <t>-49,07; 118,76</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 8,84</t>
+          <t>-4,76; 8,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 18,6</t>
+          <t>2,9; 18,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,68; 22,24</t>
+          <t>8,69; 21,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,49; 19,19</t>
+          <t>10,57; 18,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 66,46</t>
+          <t>-22,56; 67,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,62; 108,83</t>
+          <t>11,6; 104,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,37; 235,59</t>
+          <t>52,78; 228,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>72,35; 206,95</t>
+          <t>73,4; 202,21</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,69</t>
+          <t>2,14; 4,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,08</t>
+          <t>6,2; 9,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,52</t>
+          <t>4,75; 7,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,69</t>
+          <t>3,01; 6,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,8; 85,8</t>
+          <t>31,87; 86,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>75,82; 139,57</t>
+          <t>79,9; 142,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,81; 138,51</t>
+          <t>70,94; 138,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,35; 139,21</t>
+          <t>48,89; 143,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1001-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1001-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>195,83%</t>
+          <t>183,4%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,22</t>
+          <t>-2,04; 2,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,1</t>
+          <t>0,48; 5,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,16</t>
+          <t>-1,49; 3,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 11,19</t>
+          <t>0,48; 10,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,18; 157,68</t>
+          <t>-56,21; 160,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 445,11</t>
+          <t>4,86; 399,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,37; 251,86</t>
+          <t>-49,67; 228,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,9; 1210,94</t>
+          <t>-12,06; 1035,59</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,31</t>
+          <t>3,8</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>141,53%</t>
+          <t>155,08%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,65</t>
+          <t>1,73; 6,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,79</t>
+          <t>0,25; 5,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 2,98</t>
+          <t>-2,03; 2,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 6,56</t>
+          <t>1,02; 7,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,05; 274,2</t>
+          <t>38,44; 273,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 244,64</t>
+          <t>1,66; 253,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,29; 93,63</t>
+          <t>-36,63; 86,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 552,51</t>
+          <t>13,22; 594,72</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,04</t>
+          <t>0,0; 5,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 9,48</t>
+          <t>2,65; 9,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,7</t>
+          <t>-0,45; 4,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,5</t>
+          <t>-2,05; 3,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 172,95</t>
+          <t>-5,02; 170,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,68; 217,52</t>
+          <t>33,55; 212,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 134,99</t>
+          <t>-8,66; 132,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-37,83; 58,72</t>
+          <t>-28,02; 81,74</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,13</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 8,55</t>
+          <t>1,42; 8,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 10,42</t>
+          <t>2,63; 10,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,7</t>
+          <t>0,1; 6,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,09</t>
+          <t>-0,32; 4,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,62; 180,77</t>
+          <t>16,3; 163,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,17; 193,32</t>
+          <t>29,85; 193,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 127,27</t>
+          <t>-2,1; 121,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,71; 324,41</t>
+          <t>-3,97; 99,22</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>6,32</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 6,8</t>
+          <t>-1,56; 6,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 15,44</t>
+          <t>6,07; 16,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,92; 15,23</t>
+          <t>6,56; 15,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,59</t>
+          <t>3,28; 9,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 107,96</t>
+          <t>-14,95; 104,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,83; 205,09</t>
+          <t>51,16; 212,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,0; 315,42</t>
+          <t>72,29; 294,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,45; 147,11</t>
+          <t>36,59; 168,25</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>104,27%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 7,6</t>
+          <t>-3,18; 7,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,61; 16,71</t>
+          <t>4,83; 16,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,87; 18,9</t>
+          <t>7,83; 19,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 8,34</t>
+          <t>4,51; 11,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,68; 81,94</t>
+          <t>-21,19; 70,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,2; 185,84</t>
+          <t>30,74; 179,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72,15; 300,46</t>
+          <t>66,89; 304,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,07; 118,76</t>
+          <t>46,17; 183,9</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>126,32%</t>
+          <t>121,15%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 8,6</t>
+          <t>-5,13; 8,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 18,31</t>
+          <t>4,21; 19,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,69; 21,69</t>
+          <t>8,54; 21,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,57; 18,91</t>
+          <t>10,08; 18,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,56; 67,68</t>
+          <t>-25,25; 61,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,6; 104,75</t>
+          <t>13,86; 106,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,78; 228,34</t>
+          <t>54,28; 214,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>73,4; 202,21</t>
+          <t>66,0; 189,86</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>5,7</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,75</t>
+          <t>2,08; 4,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,27</t>
+          <t>6,11; 8,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,75; 7,49</t>
+          <t>4,64; 7,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,69</t>
+          <t>4,5; 6,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,87; 86,4</t>
+          <t>31,78; 87,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,9; 142,72</t>
+          <t>78,56; 141,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,94; 138,12</t>
+          <t>69,69; 139,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>48,89; 143,9</t>
+          <t>65,56; 125,88</t>
         </is>
       </c>
     </row>
